--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.91055423023607</v>
+        <v>5.835465062413362</v>
       </c>
       <c r="D2" t="n">
-        <v>28.58931208392568</v>
+        <v>4.645763213637923</v>
       </c>
       <c r="E2" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F2" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.89240541168653</v>
+        <v>4.695015879399061</v>
       </c>
       <c r="D3" t="n">
-        <v>17.92310392540833</v>
+        <v>2.912504387878855</v>
       </c>
       <c r="E3" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F3" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.7782100092027</v>
+        <v>3.863959126495438</v>
       </c>
       <c r="D4" t="n">
-        <v>33.85332424222779</v>
+        <v>5.501165189362015</v>
       </c>
       <c r="E4" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F4" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.58923186924987</v>
+        <v>3.345750178753104</v>
       </c>
       <c r="D5" t="n">
-        <v>42.93704241793507</v>
+        <v>6.97726939291445</v>
       </c>
       <c r="E5" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F5" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.72316140032819</v>
+        <v>1.742513727553332</v>
       </c>
       <c r="D6" t="n">
-        <v>27.44343070625247</v>
+        <v>4.459557489766027</v>
       </c>
       <c r="E6" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F6" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.634621299204037</v>
+        <v>1.565625961120656</v>
       </c>
       <c r="D7" t="n">
-        <v>1.823054966742559</v>
+        <v>0.2962464320956659</v>
       </c>
       <c r="E7" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F7" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.20013717363049</v>
+        <v>2.632522290714954</v>
       </c>
       <c r="D8" t="n">
-        <v>26.4379660598677</v>
+        <v>4.296169484728501</v>
       </c>
       <c r="E8" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F8" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.10733633493889</v>
+        <v>7.004942154427569</v>
       </c>
       <c r="D9" t="n">
-        <v>63.29707398052821</v>
+        <v>10.28577452183583</v>
       </c>
       <c r="E9" t="n">
-        <v>11.09501318396979</v>
+        <v>1.802939642395091</v>
       </c>
       <c r="F9" t="n">
-        <v>16.77517661310967</v>
+        <v>2.725966199630322</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
